--- a/범운해운항공_전체데이터_통합백업_2026-10-22.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-22.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE65"/>
+  <dimension ref="A1:AE66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8588,6 +8588,139 @@
       </c>
       <c r="AE65" t="n">
         <v>32</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BW-2026-069</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>BW260018</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>맥익스프레스 인터내셔날(주)</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>金皓</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>위해신노통관사</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>해상(LCL)</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0.000 CBM</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>295</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>295</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T66" t="n">
+        <v>590000</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1475000</v>
+      </c>
+      <c r="V66" t="n">
+        <v>-885000</v>
+      </c>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>山东省威海市环翠区怡园街道抚顺路 高发大厦 主楼 C区 401</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13906301025</t>
+        </is>
+      </c>
+      <c r="AC66" t="n">
+        <v>295</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>295</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -9272,7 +9405,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 38000, "1CBM당단가": 0}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "케이글로발"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "케이글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18000, "추가단가": 18000, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "케이글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 38000, "1CBM당단가": 0}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "케이글로발", "위해신노통관사"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "케이글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18000, "추가단가": 18000, "1CBM당단가": 0}}}}, "위해신노통관사": {"중국": {"해상(LCL)": {"일반화물": {"기본중량": 1.0, "기본요금": 5000, "추가단가": 5000, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "케이글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "위해신노통관사": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "인천"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-22.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-22.xlsx
@@ -8683,13 +8683,13 @@
         </is>
       </c>
       <c r="T66" t="n">
-        <v>590000</v>
+        <v>5900000</v>
       </c>
       <c r="U66" t="n">
         <v>1475000</v>
       </c>
       <c r="V66" t="n">
-        <v>-885000</v>
+        <v>4425000</v>
       </c>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr">

--- a/범운해운항공_전체데이터_통합백업_2026-10-22.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-22.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE66"/>
+  <dimension ref="A1:AE69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8721,6 +8721,405 @@
       </c>
       <c r="AE66" t="n">
         <v>295</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BW-2026-070</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>BW260019</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>글로우필메디앤코</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gina Sylvester </t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>22×19×10cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0.005 CBM</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T67" t="n">
+        <v>39840</v>
+      </c>
+      <c r="U67" t="n">
+        <v>35000</v>
+      </c>
+      <c r="V67" t="n">
+        <v>4840</v>
+      </c>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>1093 Hawthorne Avenue, Beecher, IL 60401</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>1-708-595-3553</t>
+        </is>
+      </c>
+      <c r="AC67" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BW-2026-071</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>BW260020</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>글로우필메디앤코</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Renay Scott</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>34×20×20cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0.014 CBM</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>3</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T68" t="n">
+        <v>119520</v>
+      </c>
+      <c r="U68" t="n">
+        <v>85000</v>
+      </c>
+      <c r="V68" t="n">
+        <v>34520</v>
+      </c>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>619 Belleville Avenue Belleville, NJ 07109</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>1-862-336-5797</t>
+        </is>
+      </c>
+      <c r="AC68" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BW-2026-072</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>BW260021</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>글로우필메디앤코</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brenda A </t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>24×20×10cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0.005 CBM</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T69" t="n">
+        <v>39840</v>
+      </c>
+      <c r="U69" t="n">
+        <v>35000</v>
+      </c>
+      <c r="V69" t="n">
+        <v>4840</v>
+      </c>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>11537 Lago De Garda Dr Austin, TX 78747</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>1-512-489-7880</t>
+        </is>
+      </c>
+      <c r="AC69" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/범운해운항공_전체데이터_통합백업_2026-10-22.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-22.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE69"/>
+  <dimension ref="A1:AE71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr"/>
@@ -9120,6 +9120,272 @@
       </c>
       <c r="AE69" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BW-2026-073</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>BW260022</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>아코글로벌</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Mylene Marquez</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>28×28×28cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0.022 CBM</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>4</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T70" t="n">
+        <v>199200</v>
+      </c>
+      <c r="U70" t="n">
+        <v>110000</v>
+      </c>
+      <c r="V70" t="n">
+        <v>89200</v>
+      </c>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>Your Spa LLC 18832 Christina Avenue Cerritos, CA 90703 United States</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>+1 (562) 412-4328</t>
+        </is>
+      </c>
+      <c r="AC70" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BW-2026-074</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>BW260023</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>아코글로벌</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Jose Fernandez</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>26×18×15cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0.008 CBM</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>2</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T71" t="n">
+        <v>79680</v>
+      </c>
+      <c r="U71" t="n">
+        <v>60000</v>
+      </c>
+      <c r="V71" t="n">
+        <v>19680</v>
+      </c>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>99 Van Buren St Newark NJ 07105 United States</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>+1 (609) 331-6550</t>
+        </is>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
